--- a/imports/registry-lab/data/agriculture/livestock-registry.xlsx
+++ b/imports/registry-lab/data/agriculture/livestock-registry.xlsx
@@ -1695,17 +1695,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1726,25 +1727,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>effective_from</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>effective_until</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>declared_by_office</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>district_code</t>
         </is>
@@ -1768,21 +1774,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>cattle</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="F2" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>National Animal Health Authority</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>D-NORTH</t>
         </is>
@@ -1806,21 +1817,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>cattle</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>expired</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="F3" s="1" t="n">
         <v>45870</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>National Animal Health Authority</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>D-CENTRAL</t>
         </is>
@@ -2038,17 +2054,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,35 +2080,60 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>application_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>herd_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>origin_premises_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>destination_premises_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>origin_district</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>origin_district_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>destination_district</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>destination_district_code</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>permit_status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>issued_on</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>valid_until</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>revoked_on</t>
         </is>
@@ -2101,28 +2147,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>MAPP-2001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>HERD-2001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PREM-2001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PREM-DEST-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Central Grazing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>D-CENTRAL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>South Plains</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>D-SOUTH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>46101</v>
       </c>
     </row>
